--- a/public/tests/case_simple.xlsx
+++ b/public/tests/case_simple.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C929A62-11F4-466C-BD64-E8353A013020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB7C1CC-F8A8-444B-A7B6-3A5FCD194F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
+    <sheet name="Portfolios" sheetId="2" r:id="rId2"/>
+    <sheet name="Assets" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -45,22 +47,37 @@
     <t>end</t>
   </si>
   <si>
-    <t>portfolio_sheet</t>
-  </si>
-  <si>
-    <t>Test1</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>assets_sheet</t>
-  </si>
-  <si>
-    <t>Asset1</t>
-  </si>
-  <si>
-    <t>Asset2</t>
+    <t>portfolios_source</t>
+  </si>
+  <si>
+    <t>assets_source</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>The first asset</t>
+  </si>
+  <si>
+    <t>The second asset</t>
+  </si>
+  <si>
+    <t>Portfolios</t>
+  </si>
+  <si>
+    <t>Port1</t>
+  </si>
+  <si>
+    <t>Port2</t>
   </si>
 </sst>
 </file>
@@ -104,10 +121,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,10 +406,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -432,31 +450,92 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="B2" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
